--- a/data/crops/lu_c_factor_reducedtillage.xlsx
+++ b/data/crops/lu_c_factor_reducedtillage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://worldwildlifefund-my.sharepoint.com/personal/cristobal_loyola_wwfus_org/Documents/Documents/203. Python projects/SBTN_Test/data/crops/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="61" documentId="8_{DE03094A-62C0-4937-830E-90DB4B2587C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30C80418-6B5C-4B41-8CB3-B6762B6B89A6}"/>
+  <xr:revisionPtr revIDLastSave="80" documentId="8_{DE03094A-62C0-4937-830E-90DB4B2587C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23CA4FE6-E8DD-452E-9DEE-20707912625C}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{AD288E80-6FC1-4BDD-A593-FC9351635447}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <externalReference r:id="rId2"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$O$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$O$27</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="80">
   <si>
     <t>file_name</t>
   </si>
@@ -86,9 +86,6 @@
     <t>lu_Irrigated_Barley_residues_left_on_the_field.tif</t>
   </si>
   <si>
-    <t>../data/land_use/lu_Irrigated_Barley_residues_left_on_the_field.tif</t>
-  </si>
-  <si>
     <t>Barley</t>
   </si>
   <si>
@@ -113,33 +110,21 @@
     <t>lu_Irrigated_Barley_residues_removed_from_the_field.tif</t>
   </si>
   <si>
-    <t>../data/land_use/lu_Irrigated_Barley_residues_removed_from_the_field.tif</t>
-  </si>
-  <si>
     <t>off</t>
   </si>
   <si>
     <t>lu_Irrigated_Maize_residues_left_on_the_field.tif</t>
   </si>
   <si>
-    <t>../data/land_use/lu_Irrigated_Maize_residues_left_on_the_field.tif</t>
-  </si>
-  <si>
     <t>Maize</t>
   </si>
   <si>
     <t>lu_Irrigated_Maize_residues_removed_from_the_field.tif</t>
   </si>
   <si>
-    <t>../data/land_use/lu_Irrigated_Maize_residues_removed_from_the_field.tif</t>
-  </si>
-  <si>
     <t>lu_Irrigated_Rapeseed_residues_left_on_the_field.tif</t>
   </si>
   <si>
-    <t>../data/land_use/lu_Irrigated_Rapeseed_residues_left_on_the_field.tif</t>
-  </si>
-  <si>
     <t>Rapeseed</t>
   </si>
   <si>
@@ -149,15 +134,9 @@
     <t>lu_Irrigated_Rapeseed_residues_removed_from_the_field.tif</t>
   </si>
   <si>
-    <t>../data/land_use/lu_Irrigated_Rapeseed_residues_removed_from_the_field.tif</t>
-  </si>
-  <si>
     <t>lu_Irrigated_Sorghum_residues_left_on_the_field.tif</t>
   </si>
   <si>
-    <t>../data/land_use/lu_Irrigated_Sorghum_residues_left_on_the_field.tif</t>
-  </si>
-  <si>
     <t>Sorghum</t>
   </si>
   <si>
@@ -170,75 +149,42 @@
     <t>lu_Irrigated_Sorghum_residues_removed_from_the_field.tif</t>
   </si>
   <si>
-    <t>../data/land_use/lu_Irrigated_Sorghum_residues_removed_from_the_field.tif</t>
-  </si>
-  <si>
     <t>lu_Irrigated_Wheat_residues_left_on_the_field.tif</t>
   </si>
   <si>
-    <t>../data/land_use/lu_Irrigated_Wheat_residues_left_on_the_field.tif</t>
-  </si>
-  <si>
     <t>Wheat</t>
   </si>
   <si>
     <t>lu_Irrigated_Wheat_residues_removed_from_the_field.tif</t>
   </si>
   <si>
-    <t>../data/land_use/lu_Irrigated_Wheat_residues_removed_from_the_field.tif</t>
-  </si>
-  <si>
     <t>lu_Rainfed_Barley_residues_left_on_the_field.tif</t>
   </si>
   <si>
-    <t>../data/land_use/lu_Rainfed_Barley_residues_left_on_the_field.tif</t>
-  </si>
-  <si>
     <t>Rainfed</t>
   </si>
   <si>
     <t>lu_Rainfed_Barley_residues_removed_from_the_field.tif</t>
   </si>
   <si>
-    <t>../data/land_use/lu_Rainfed_Barley_residues_removed_from_the_field.tif</t>
-  </si>
-  <si>
     <t>lu_Rainfed_Maize_residues_left_on_the_field.tif</t>
   </si>
   <si>
-    <t>../data/land_use/lu_Rainfed_Maize_residues_left_on_the_field.tif</t>
-  </si>
-  <si>
     <t>lu_Rainfed_Maize_residues_removed_from_the_field.tif</t>
   </si>
   <si>
-    <t>../data/land_use/lu_Rainfed_Maize_residues_removed_from_the_field.tif</t>
-  </si>
-  <si>
     <t>lu_Rainfed_Rapeseed_residues_left_on_the_field.tif</t>
   </si>
   <si>
-    <t>../data/land_use/lu_Rainfed_Rapeseed_residues_left_on_the_field.tif</t>
-  </si>
-  <si>
     <t>lu_Rainfed_Rapeseed_residues_removed_from_the_field.tif</t>
   </si>
   <si>
-    <t>../data/land_use/lu_Rainfed_Rapeseed_residues_removed_from_the_field.tif</t>
-  </si>
-  <si>
     <t>lu_Rainfed_Sorghum_residues_left_on_the_field.tif</t>
   </si>
   <si>
-    <t>../data/land_use/lu_Rainfed_Sorghum_residues_left_on_the_field.tif</t>
-  </si>
-  <si>
     <t>lu_Rainfed_Sorghum_residues_removed_from_the_field.tif</t>
   </si>
   <si>
-    <t>../data/land_use/lu_Rainfed_Sorghum_residues_removed_from_the_field.tif</t>
-  </si>
-  <si>
     <t>tillage</t>
   </si>
   <si>
@@ -251,9 +197,6 @@
     <t>lu_Irrigated_cotton.tif</t>
   </si>
   <si>
-    <t>../data/land_use/lu_Irrigated_cotton.tif</t>
-  </si>
-  <si>
     <t>Cotton</t>
   </si>
   <si>
@@ -263,15 +206,9 @@
     <t>lu_Rainfed_cotton.tif</t>
   </si>
   <si>
-    <t>../data/land_use/lu_Rainfed_cotton.tif</t>
-  </si>
-  <si>
     <t>lu_Irrigated_Soybeans.tif</t>
   </si>
   <si>
-    <t>../data/land_use/lu_Irrigated_Soybeans.tif</t>
-  </si>
-  <si>
     <t>Soybeans</t>
   </si>
   <si>
@@ -281,34 +218,70 @@
     <t>lu_Irrigated_Sunflower.tif</t>
   </si>
   <si>
-    <t>../data/land_use/lu_Irrigated_Sunflower.tif</t>
-  </si>
-  <si>
     <t>Sunflower</t>
   </si>
   <si>
     <t>lu_Rainfed_Soybeans.tif</t>
   </si>
   <si>
-    <t>../data/land_use/lu_Rainfed_Soybeans.tif</t>
-  </si>
-  <si>
     <t>lu_Rainfed_Sunflower.tif</t>
   </si>
   <si>
-    <t>../data/land_use/lu_Rainfed_Sunflower.tif</t>
-  </si>
-  <si>
     <t>lu_Rainfed_Wheat_residues_left_on_the_field.tif</t>
   </si>
   <si>
-    <t>../data/land_use/lu_Rainfed_Wheat_residues_left_on_the_field.tif</t>
-  </si>
-  <si>
     <t>lu_Rainfed_Wheat_residues_removed_from_the_field.tif</t>
   </si>
   <si>
-    <t>../data/land_use/lu_Rainfed_Wheat_residues_removed_from_the_field.tif</t>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Barley_irr_ron.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Maize_irr_ron.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Rapeseed_irr_ron.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Sorghum_irr_ron.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Wheat_irr_roff.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Cotton_irr.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Soybean_irr.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Sunflower_irr.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Barley_rf_ron.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Barley_rf_roff.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Maize_rf.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Rapeseed_rf_ron.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Sorghum_rf.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Cotton_rf.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Soybean_rf.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Sunflower_rf.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Wheat_rf_roff.tif</t>
   </si>
 </sst>
 </file>
@@ -401,7 +374,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -412,6 +385,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -798,7 +777,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>6</v>
@@ -819,7 +798,7 @@
         <v>11</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="O1" s="3" t="s">
         <v>12</v>
@@ -834,31 +813,31 @@
         <v>Barley_irr_ron_rt</v>
       </c>
       <c r="C2" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="F2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>17</v>
-      </c>
       <c r="G2" s="5" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="K2" s="5" t="s">
         <v>20</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>21</v>
       </c>
       <c r="L2" s="5">
         <v>0.2</v>
@@ -870,44 +849,44 @@
         <v>0.35</v>
       </c>
       <c r="O2" s="5">
-        <f>+N2*M2*L2</f>
+        <f t="shared" ref="O2:O27" si="0">+N2*M2*L2</f>
         <v>6.1600000000000002E-2</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="5" t="str">
+        <f t="shared" ref="B3:B27" si="1">+D3&amp;IF(E3="Irrigated","_irr","_rf")&amp;IF(F3="on","_ron",IF(F3="off","_roff",""))&amp;"_rt"</f>
+        <v>Barley_irr_roff_rt</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="5" t="str">
-        <f t="shared" ref="B3:B27" si="0">+D3&amp;IF(E3="Irrigated","_irr","_rf")&amp;IF(F3="on","_ron",IF(F3="off","_roff",""))&amp;"_rt"</f>
-        <v>Barley_irr_roff_rt</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>24</v>
-      </c>
       <c r="G3" s="8" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="K3" s="8" t="s">
         <v>20</v>
-      </c>
-      <c r="K3" s="8" t="s">
-        <v>21</v>
       </c>
       <c r="L3" s="8">
         <v>0.2</v>
@@ -919,44 +898,44 @@
         <v>0.35</v>
       </c>
       <c r="O3" s="8">
-        <f>+N3*M3*L3</f>
+        <f t="shared" si="0"/>
         <v>6.9999999999999993E-2</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="B4" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Barley_rf_ron_rt</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I4" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="K4" s="5" t="s">
         <v>20</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>21</v>
       </c>
       <c r="L4" s="5">
         <v>0.2</v>
@@ -968,44 +947,44 @@
         <v>0.35</v>
       </c>
       <c r="O4" s="5">
-        <f>+N4*M4*L4</f>
+        <f t="shared" si="0"/>
         <v>6.1600000000000002E-2</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="B5" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Barley_rf_roff_rt</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I5" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="J5" s="8" t="s">
+      <c r="K5" s="8" t="s">
         <v>20</v>
-      </c>
-      <c r="K5" s="8" t="s">
-        <v>21</v>
       </c>
       <c r="L5" s="8">
         <v>0.2</v>
@@ -1017,44 +996,44 @@
         <v>0.35</v>
       </c>
       <c r="O5" s="8">
-        <f>+N5*M5*L5</f>
+        <f t="shared" si="0"/>
         <v>6.9999999999999993E-2</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B6" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Maize_irr_ron_rt</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>26</v>
+      <c r="C6" s="8" t="s">
+        <v>64</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E6" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="5" t="s">
-        <v>17</v>
-      </c>
       <c r="G6" s="5" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I6" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J6" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="J6" s="5" t="s">
-        <v>20</v>
-      </c>
       <c r="K6" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="L6" s="5">
         <v>0.38</v>
@@ -1066,44 +1045,44 @@
         <v>0.35</v>
       </c>
       <c r="O6" s="5">
-        <f>+N6*M6*L6</f>
+        <f t="shared" si="0"/>
         <v>0.11704000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B7" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Maize_irr_roff_rt</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F7" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="K7" s="8" t="s">
         <v>24</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="J7" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="K7" s="8" t="s">
-        <v>27</v>
       </c>
       <c r="L7" s="8">
         <v>0.38</v>
@@ -1115,44 +1094,44 @@
         <v>0.35</v>
       </c>
       <c r="O7" s="8">
-        <f>+N7*M7*L7</f>
+        <f t="shared" si="0"/>
         <v>0.13299999999999998</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="B8" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Maize_rf_ron_rt</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>54</v>
+      <c r="C8" s="10" t="s">
+        <v>73</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J8" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="J8" s="5" t="s">
-        <v>20</v>
-      </c>
       <c r="K8" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="L8" s="5">
         <v>0.38</v>
@@ -1164,44 +1143,44 @@
         <v>0.35</v>
       </c>
       <c r="O8" s="5">
-        <f>+N8*M8*L8</f>
+        <f t="shared" si="0"/>
         <v>0.11704000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="B9" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Maize_rf_roff_rt</v>
       </c>
-      <c r="C9" s="8" t="s">
-        <v>56</v>
+      <c r="C9" s="11" t="s">
+        <v>73</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="F9" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="K9" s="8" t="s">
         <v>24</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>27</v>
       </c>
       <c r="L9" s="8">
         <v>0.38</v>
@@ -1213,44 +1192,44 @@
         <v>0.35</v>
       </c>
       <c r="O9" s="8">
-        <f>+N9*M9*L9</f>
+        <f t="shared" si="0"/>
         <v>0.13299999999999998</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B10" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Rapeseed_irr_ron_rt</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E10" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="5" t="s">
-        <v>17</v>
-      </c>
       <c r="G10" s="5" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L10" s="5">
         <v>0.25</v>
@@ -1262,44 +1241,44 @@
         <v>0.35</v>
       </c>
       <c r="O10" s="5">
-        <f>+N10*M10*L10</f>
+        <f t="shared" si="0"/>
         <v>7.6999999999999999E-2</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B11" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Rapeseed_irr_roff_rt</v>
       </c>
-      <c r="C11" s="8" t="s">
-        <v>35</v>
+      <c r="C11" s="5" t="s">
+        <v>65</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L11" s="8">
         <v>0.25</v>
@@ -1311,44 +1290,44 @@
         <v>0.35</v>
       </c>
       <c r="O11" s="8">
-        <f>+N11*M11*L11</f>
+        <f t="shared" si="0"/>
         <v>8.7499999999999994E-2</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="B12" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Rapeseed_rf_ron_rt</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>58</v>
+      <c r="C12" s="11" t="s">
+        <v>74</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L12" s="5">
         <v>0.25</v>
@@ -1360,44 +1339,44 @@
         <v>0.35</v>
       </c>
       <c r="O12" s="5">
-        <f>+N12*M12*L12</f>
+        <f t="shared" si="0"/>
         <v>7.6999999999999999E-2</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A13" s="7" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="B13" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Rapeseed_rf_roff_rt</v>
       </c>
-      <c r="C13" s="8" t="s">
-        <v>60</v>
+      <c r="C13" s="10" t="s">
+        <v>74</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L13" s="8">
         <v>0.25</v>
@@ -1409,44 +1388,44 @@
         <v>0.35</v>
       </c>
       <c r="O13" s="8">
-        <f>+N13*M13*L13</f>
+        <f t="shared" si="0"/>
         <v>8.7499999999999994E-2</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B14" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Sorghum_irr_ron_rt</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>37</v>
+      <c r="C14" s="8" t="s">
+        <v>66</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E14" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F14" s="5" t="s">
-        <v>17</v>
-      </c>
       <c r="G14" s="5" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="L14" s="5">
         <v>0.1</v>
@@ -1458,44 +1437,44 @@
         <v>0.35</v>
       </c>
       <c r="O14" s="5">
-        <f>+N14*M14*L14</f>
+        <f t="shared" si="0"/>
         <v>3.0800000000000001E-2</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A15" s="7" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B15" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Sorghum_irr_roff_rt</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="L15" s="8">
         <v>0.1</v>
@@ -1507,44 +1486,44 @@
         <v>0.35</v>
       </c>
       <c r="O15" s="8">
-        <f>+N15*M15*L15</f>
+        <f t="shared" si="0"/>
         <v>3.4999999999999996E-2</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="B16" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Sorghum_rf_ron_rt</v>
       </c>
-      <c r="C16" s="5" t="s">
-        <v>62</v>
+      <c r="C16" s="10" t="s">
+        <v>75</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="L16" s="5">
         <v>0.1</v>
@@ -1556,44 +1535,44 @@
         <v>0.35</v>
       </c>
       <c r="O16" s="5">
-        <f>+N16*M16*L16</f>
+        <f t="shared" si="0"/>
         <v>3.0800000000000001E-2</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A17" s="7" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="B17" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Sorghum_rf_roff_rt</v>
       </c>
-      <c r="C17" s="8" t="s">
-        <v>64</v>
+      <c r="C17" s="11" t="s">
+        <v>75</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="K17" s="8" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="L17" s="8">
         <v>0.1</v>
@@ -1605,44 +1584,44 @@
         <v>0.35</v>
       </c>
       <c r="O17" s="8">
-        <f>+N17*M17*L17</f>
+        <f t="shared" si="0"/>
         <v>3.4999999999999996E-2</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="B18" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Wheat_irr_ron_rt</v>
       </c>
-      <c r="C18" s="5" t="s">
-        <v>44</v>
+      <c r="C18" s="8" t="s">
+        <v>67</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E18" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F18" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F18" s="5" t="s">
-        <v>17</v>
-      </c>
       <c r="G18" s="5" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I18" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J18" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="J18" s="5" t="s">
+      <c r="K18" s="5" t="s">
         <v>20</v>
-      </c>
-      <c r="K18" s="5" t="s">
-        <v>21</v>
       </c>
       <c r="L18" s="5">
         <v>0.2</v>
@@ -1654,44 +1633,44 @@
         <v>0.35</v>
       </c>
       <c r="O18" s="5">
-        <f>+N18*M18*L18</f>
+        <f t="shared" si="0"/>
         <v>6.1600000000000002E-2</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A19" s="7" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="B19" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Wheat_irr_roff_rt</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I19" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="J19" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="J19" s="8" t="s">
+      <c r="K19" s="8" t="s">
         <v>20</v>
-      </c>
-      <c r="K19" s="8" t="s">
-        <v>21</v>
       </c>
       <c r="L19" s="8">
         <v>0.2</v>
@@ -1703,44 +1682,44 @@
         <v>0.35</v>
       </c>
       <c r="O19" s="8">
-        <f>+N19*M19*L19</f>
+        <f t="shared" si="0"/>
         <v>6.9999999999999993E-2</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B20" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Cotton_irr_rt</v>
+      </c>
+      <c r="C20" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="B20" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>Cotton_irr_rt</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>69</v>
-      </c>
       <c r="D20" s="5" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="L20" s="5">
         <v>0.4</v>
@@ -1752,44 +1731,44 @@
         <v>0.35</v>
       </c>
       <c r="O20" s="8">
-        <f>+N20*M20*L20</f>
+        <f t="shared" si="0"/>
         <v>0.13999999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A21" s="7" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="B21" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Cotton_rf_rt</v>
       </c>
-      <c r="C21" s="8" t="s">
-        <v>73</v>
+      <c r="C21" s="5" t="s">
+        <v>76</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J21" s="8" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="L21" s="8">
         <v>0.4</v>
@@ -1801,44 +1780,44 @@
         <v>0.35</v>
       </c>
       <c r="O21" s="8">
-        <f>+N21*M21*L21</f>
+        <f t="shared" si="0"/>
         <v>0.13999999999999999</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="B22" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Soybeans_irr_rt</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L22" s="5">
         <v>0.32</v>
@@ -1850,44 +1829,44 @@
         <v>0.35</v>
       </c>
       <c r="O22" s="8">
-        <f>+N22*M22*L22</f>
+        <f t="shared" si="0"/>
         <v>0.11199999999999999</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A23" s="7" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="B23" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Sunflower_irr_rt</v>
       </c>
-      <c r="C23" s="8" t="s">
-        <v>79</v>
+      <c r="C23" s="5" t="s">
+        <v>70</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J23" s="8" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="K23" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L23" s="8">
         <v>0.25</v>
@@ -1899,44 +1878,44 @@
         <v>0.35</v>
       </c>
       <c r="O23" s="8">
-        <f>+N23*M23*L23</f>
+        <f t="shared" si="0"/>
         <v>8.7499999999999994E-2</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="B24" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Soybeans_rf_rt</v>
       </c>
-      <c r="C24" s="5" t="s">
-        <v>82</v>
+      <c r="C24" s="10" t="s">
+        <v>77</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="K24" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L24" s="5">
         <v>0.32</v>
@@ -1948,44 +1927,44 @@
         <v>0.35</v>
       </c>
       <c r="O24" s="8">
-        <f>+N24*M24*L24</f>
+        <f t="shared" si="0"/>
         <v>0.11199999999999999</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A25" s="7" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="B25" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Sunflower_rf_rt</v>
       </c>
-      <c r="C25" s="8" t="s">
-        <v>84</v>
+      <c r="C25" s="10" t="s">
+        <v>78</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J25" s="8" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="K25" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L25" s="8">
         <v>0.25</v>
@@ -1997,47 +1976,47 @@
         <v>0.35</v>
       </c>
       <c r="O25" s="8">
-        <f>+N25*M25*L25</f>
+        <f t="shared" si="0"/>
         <v>8.7499999999999994E-2</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="B26" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Wheat_rf_ron_rt</v>
       </c>
-      <c r="C26" s="5" t="s">
-        <v>86</v>
+      <c r="C26" s="10" t="s">
+        <v>79</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G26" s="5" t="str">
         <f>+_xlfn.XLOOKUP($D26,$D$11:$D$43,G$11:G$43,"missing",0)</f>
         <v>reduced</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I26" s="5" t="str">
-        <f>+_xlfn.XLOOKUP($D26,$D$11:$D$43,I$11:I$43,"missing",0)</f>
+        <f t="shared" ref="I26:K27" si="2">+_xlfn.XLOOKUP($D26,$D$11:$D$43,I$11:I$43,"missing",0)</f>
         <v>annual</v>
       </c>
       <c r="J26" s="5" t="str">
-        <f>+_xlfn.XLOOKUP($D26,$D$11:$D$43,J$11:J$43,"missing",0)</f>
+        <f t="shared" si="2"/>
         <v>Cereals</v>
       </c>
       <c r="K26" s="5" t="str">
-        <f>+_xlfn.XLOOKUP($D26,$D$11:$D$43,K$11:K$43,"missing",0)</f>
+        <f t="shared" si="2"/>
         <v>Various</v>
       </c>
       <c r="L26" s="5">
@@ -2052,47 +2031,47 @@
         <v>0.35</v>
       </c>
       <c r="O26" s="8">
-        <f>+N26*M26*L26</f>
+        <f t="shared" si="0"/>
         <v>4.6199999999999998E-2</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A27" s="7" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="B27" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Wheat_rf_roff_rt</v>
       </c>
-      <c r="C27" s="8" t="s">
-        <v>88</v>
+      <c r="C27" s="11" t="s">
+        <v>79</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G27" s="8" t="str">
         <f>+_xlfn.XLOOKUP($D27,$D$11:$D$43,G$11:G$43,"missing",0)</f>
         <v>reduced</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I27" s="8" t="str">
-        <f>+_xlfn.XLOOKUP($D27,$D$11:$D$43,I$11:I$43,"missing",0)</f>
+        <f t="shared" si="2"/>
         <v>annual</v>
       </c>
       <c r="J27" s="8" t="str">
-        <f>+_xlfn.XLOOKUP($D27,$D$11:$D$43,J$11:J$43,"missing",0)</f>
+        <f t="shared" si="2"/>
         <v>Cereals</v>
       </c>
       <c r="K27" s="8" t="str">
-        <f>+_xlfn.XLOOKUP($D27,$D$11:$D$43,K$11:K$43,"missing",0)</f>
+        <f t="shared" si="2"/>
         <v>Various</v>
       </c>
       <c r="L27" s="8">
@@ -2106,12 +2085,12 @@
         <v>0.35</v>
       </c>
       <c r="O27" s="8">
-        <f>+N27*M27*L27</f>
+        <f t="shared" si="0"/>
         <v>0.105</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O19" xr:uid="{C3D563D1-830A-486E-AE30-CC87FDA7651F}">
+  <autoFilter ref="A1:O27" xr:uid="{C3D563D1-830A-486E-AE30-CC87FDA7651F}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O19">
       <sortCondition ref="D1:D19"/>
     </sortState>

--- a/data/crops/lu_c_factor_reducedtillage.xlsx
+++ b/data/crops/lu_c_factor_reducedtillage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://worldwildlifefund-my.sharepoint.com/personal/cristobal_loyola_wwfus_org/Documents/Documents/203. Python projects/SBTN_Test/data/crops/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="80" documentId="8_{DE03094A-62C0-4937-830E-90DB4B2587C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23CA4FE6-E8DD-452E-9DEE-20707912625C}"/>
+  <xr:revisionPtr revIDLastSave="82" documentId="8_{DE03094A-62C0-4937-830E-90DB4B2587C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27DF468F-955A-40E3-B34F-D91DFFA9892B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{AD288E80-6FC1-4BDD-A593-FC9351635447}"/>
   </bookViews>
@@ -416,6 +416,7 @@
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="foreground_occupation_file_inde"/>
+      <sheetName val="Sheet1"/>
       <sheetName val="Crop_Classification"/>
       <sheetName val="C_Crops"/>
     </sheetNames>
@@ -423,6 +424,7 @@
       <sheetData sheetId="0"/>
       <sheetData sheetId="1"/>
       <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -849,7 +851,7 @@
         <v>0.35</v>
       </c>
       <c r="O2" s="5">
-        <f t="shared" ref="O2:O27" si="0">+N2*M2*L2</f>
+        <f>+N2*M2*L2</f>
         <v>6.1600000000000002E-2</v>
       </c>
     </row>
@@ -858,7 +860,7 @@
         <v>21</v>
       </c>
       <c r="B3" s="5" t="str">
-        <f t="shared" ref="B3:B27" si="1">+D3&amp;IF(E3="Irrigated","_irr","_rf")&amp;IF(F3="on","_ron",IF(F3="off","_roff",""))&amp;"_rt"</f>
+        <f t="shared" ref="B3:B27" si="0">+D3&amp;IF(E3="Irrigated","_irr","_rf")&amp;IF(F3="on","_ron",IF(F3="off","_roff",""))&amp;"_rt"</f>
         <v>Barley_irr_roff_rt</v>
       </c>
       <c r="C3" s="5" t="s">
@@ -898,7 +900,7 @@
         <v>0.35</v>
       </c>
       <c r="O3" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="O3:O27" si="1">+N3*M3*L3</f>
         <v>6.9999999999999993E-2</v>
       </c>
     </row>
@@ -907,7 +909,7 @@
         <v>38</v>
       </c>
       <c r="B4" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Barley_rf_ron_rt</v>
       </c>
       <c r="C4" s="5" t="s">
@@ -947,7 +949,7 @@
         <v>0.35</v>
       </c>
       <c r="O4" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.1600000000000002E-2</v>
       </c>
     </row>
@@ -956,7 +958,7 @@
         <v>40</v>
       </c>
       <c r="B5" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Barley_rf_roff_rt</v>
       </c>
       <c r="C5" s="8" t="s">
@@ -996,7 +998,7 @@
         <v>0.35</v>
       </c>
       <c r="O5" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.9999999999999993E-2</v>
       </c>
     </row>
@@ -1005,7 +1007,7 @@
         <v>23</v>
       </c>
       <c r="B6" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Maize_irr_ron_rt</v>
       </c>
       <c r="C6" s="8" t="s">
@@ -1045,7 +1047,7 @@
         <v>0.35</v>
       </c>
       <c r="O6" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.11704000000000001</v>
       </c>
     </row>
@@ -1054,7 +1056,7 @@
         <v>25</v>
       </c>
       <c r="B7" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Maize_irr_roff_rt</v>
       </c>
       <c r="C7" s="8" t="s">
@@ -1094,7 +1096,7 @@
         <v>0.35</v>
       </c>
       <c r="O7" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.13299999999999998</v>
       </c>
     </row>
@@ -1103,7 +1105,7 @@
         <v>41</v>
       </c>
       <c r="B8" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Maize_rf_ron_rt</v>
       </c>
       <c r="C8" s="10" t="s">
@@ -1143,7 +1145,7 @@
         <v>0.35</v>
       </c>
       <c r="O8" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.11704000000000001</v>
       </c>
     </row>
@@ -1152,7 +1154,7 @@
         <v>42</v>
       </c>
       <c r="B9" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Maize_rf_roff_rt</v>
       </c>
       <c r="C9" s="11" t="s">
@@ -1192,7 +1194,7 @@
         <v>0.35</v>
       </c>
       <c r="O9" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.13299999999999998</v>
       </c>
     </row>
@@ -1201,7 +1203,7 @@
         <v>26</v>
       </c>
       <c r="B10" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Rapeseed_irr_ron_rt</v>
       </c>
       <c r="C10" s="5" t="s">
@@ -1241,7 +1243,7 @@
         <v>0.35</v>
       </c>
       <c r="O10" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>7.6999999999999999E-2</v>
       </c>
     </row>
@@ -1250,7 +1252,7 @@
         <v>29</v>
       </c>
       <c r="B11" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Rapeseed_irr_roff_rt</v>
       </c>
       <c r="C11" s="5" t="s">
@@ -1290,7 +1292,7 @@
         <v>0.35</v>
       </c>
       <c r="O11" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8.7499999999999994E-2</v>
       </c>
     </row>
@@ -1299,7 +1301,7 @@
         <v>43</v>
       </c>
       <c r="B12" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Rapeseed_rf_ron_rt</v>
       </c>
       <c r="C12" s="11" t="s">
@@ -1339,7 +1341,7 @@
         <v>0.35</v>
       </c>
       <c r="O12" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>7.6999999999999999E-2</v>
       </c>
     </row>
@@ -1348,7 +1350,7 @@
         <v>44</v>
       </c>
       <c r="B13" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Rapeseed_rf_roff_rt</v>
       </c>
       <c r="C13" s="10" t="s">
@@ -1388,7 +1390,7 @@
         <v>0.35</v>
       </c>
       <c r="O13" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8.7499999999999994E-2</v>
       </c>
     </row>
@@ -1397,7 +1399,7 @@
         <v>30</v>
       </c>
       <c r="B14" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Sorghum_irr_ron_rt</v>
       </c>
       <c r="C14" s="8" t="s">
@@ -1437,7 +1439,7 @@
         <v>0.35</v>
       </c>
       <c r="O14" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3.0800000000000001E-2</v>
       </c>
     </row>
@@ -1446,7 +1448,7 @@
         <v>34</v>
       </c>
       <c r="B15" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Sorghum_irr_roff_rt</v>
       </c>
       <c r="C15" s="8" t="s">
@@ -1486,7 +1488,7 @@
         <v>0.35</v>
       </c>
       <c r="O15" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3.4999999999999996E-2</v>
       </c>
     </row>
@@ -1495,7 +1497,7 @@
         <v>45</v>
       </c>
       <c r="B16" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Sorghum_rf_ron_rt</v>
       </c>
       <c r="C16" s="10" t="s">
@@ -1535,7 +1537,7 @@
         <v>0.35</v>
       </c>
       <c r="O16" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3.0800000000000001E-2</v>
       </c>
     </row>
@@ -1544,7 +1546,7 @@
         <v>46</v>
       </c>
       <c r="B17" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Sorghum_rf_roff_rt</v>
       </c>
       <c r="C17" s="11" t="s">
@@ -1584,7 +1586,7 @@
         <v>0.35</v>
       </c>
       <c r="O17" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3.4999999999999996E-2</v>
       </c>
     </row>
@@ -1593,7 +1595,7 @@
         <v>35</v>
       </c>
       <c r="B18" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Wheat_irr_ron_rt</v>
       </c>
       <c r="C18" s="8" t="s">
@@ -1633,7 +1635,7 @@
         <v>0.35</v>
       </c>
       <c r="O18" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.1600000000000002E-2</v>
       </c>
     </row>
@@ -1642,7 +1644,7 @@
         <v>37</v>
       </c>
       <c r="B19" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Wheat_irr_roff_rt</v>
       </c>
       <c r="C19" s="8" t="s">
@@ -1682,7 +1684,7 @@
         <v>0.35</v>
       </c>
       <c r="O19" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.9999999999999993E-2</v>
       </c>
     </row>
@@ -1691,7 +1693,7 @@
         <v>50</v>
       </c>
       <c r="B20" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Cotton_irr_rt</v>
       </c>
       <c r="C20" s="8" t="s">
@@ -1731,7 +1733,7 @@
         <v>0.35</v>
       </c>
       <c r="O20" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.13999999999999999</v>
       </c>
     </row>
@@ -1740,7 +1742,7 @@
         <v>53</v>
       </c>
       <c r="B21" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Cotton_rf_rt</v>
       </c>
       <c r="C21" s="5" t="s">
@@ -1780,7 +1782,7 @@
         <v>0.35</v>
       </c>
       <c r="O21" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.13999999999999999</v>
       </c>
     </row>
@@ -1789,7 +1791,7 @@
         <v>54</v>
       </c>
       <c r="B22" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Soybeans_irr_rt</v>
       </c>
       <c r="C22" s="5" t="s">
@@ -1829,7 +1831,7 @@
         <v>0.35</v>
       </c>
       <c r="O22" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.11199999999999999</v>
       </c>
     </row>
@@ -1838,7 +1840,7 @@
         <v>57</v>
       </c>
       <c r="B23" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Sunflower_irr_rt</v>
       </c>
       <c r="C23" s="5" t="s">
@@ -1878,7 +1880,7 @@
         <v>0.35</v>
       </c>
       <c r="O23" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8.7499999999999994E-2</v>
       </c>
     </row>
@@ -1887,7 +1889,7 @@
         <v>59</v>
       </c>
       <c r="B24" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Soybeans_rf_rt</v>
       </c>
       <c r="C24" s="10" t="s">
@@ -1927,7 +1929,7 @@
         <v>0.35</v>
       </c>
       <c r="O24" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.11199999999999999</v>
       </c>
     </row>
@@ -1936,7 +1938,7 @@
         <v>60</v>
       </c>
       <c r="B25" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Sunflower_rf_rt</v>
       </c>
       <c r="C25" s="10" t="s">
@@ -1976,7 +1978,7 @@
         <v>0.35</v>
       </c>
       <c r="O25" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8.7499999999999994E-2</v>
       </c>
     </row>
@@ -1985,7 +1987,7 @@
         <v>61</v>
       </c>
       <c r="B26" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Wheat_rf_ron_rt</v>
       </c>
       <c r="C26" s="10" t="s">
@@ -2004,8 +2006,8 @@
         <f>+_xlfn.XLOOKUP($D26,$D$11:$D$43,G$11:G$43,"missing",0)</f>
         <v>reduced</v>
       </c>
-      <c r="H26" s="5" t="s">
-        <v>18</v>
+      <c r="H26" s="8" t="s">
+        <v>17</v>
       </c>
       <c r="I26" s="5" t="str">
         <f t="shared" ref="I26:K27" si="2">+_xlfn.XLOOKUP($D26,$D$11:$D$43,I$11:I$43,"missing",0)</f>
@@ -2031,7 +2033,7 @@
         <v>0.35</v>
       </c>
       <c r="O26" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4.6199999999999998E-2</v>
       </c>
     </row>
@@ -2040,7 +2042,7 @@
         <v>62</v>
       </c>
       <c r="B27" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Wheat_rf_roff_rt</v>
       </c>
       <c r="C27" s="11" t="s">
@@ -2060,7 +2062,7 @@
         <v>reduced</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I27" s="8" t="str">
         <f t="shared" si="2"/>
@@ -2085,7 +2087,7 @@
         <v>0.35</v>
       </c>
       <c r="O27" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.105</v>
       </c>
     </row>

--- a/data/crops/lu_c_factor_reducedtillage.xlsx
+++ b/data/crops/lu_c_factor_reducedtillage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://worldwildlifefund-my.sharepoint.com/personal/cristobal_loyola_wwfus_org/Documents/Documents/203. Python projects/SBTN_Test/data/crops/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="82" documentId="8_{DE03094A-62C0-4937-830E-90DB4B2587C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27DF468F-955A-40E3-B34F-D91DFFA9892B}"/>
+  <xr:revisionPtr revIDLastSave="86" documentId="8_{DE03094A-62C0-4937-830E-90DB4B2587C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A6D869F-5FC4-4115-A285-1B9618839F49}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{AD288E80-6FC1-4BDD-A593-FC9351635447}"/>
   </bookViews>
@@ -419,12 +419,14 @@
       <sheetName val="Sheet1"/>
       <sheetName val="Crop_Classification"/>
       <sheetName val="C_Crops"/>
+      <sheetName val="lu_c_factor_inventory"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
       <sheetData sheetId="1"/>
       <sheetData sheetId="2"/>
       <sheetData sheetId="3"/>
+      <sheetData sheetId="4" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -747,7 +749,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3D563D1-830A-486E-AE30-CC87FDA7651F}">
-  <dimension ref="A1:O27"/>
+  <dimension ref="A1:R27"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="49.453125" bestFit="1" customWidth="1"/>
@@ -759,7 +761,7 @@
     <col min="10" max="10" width="26.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -806,7 +808,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>13</v>
       </c>
@@ -855,7 +857,7 @@
         <v>6.1600000000000002E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A3" s="7" t="s">
         <v>21</v>
       </c>
@@ -903,8 +905,16 @@
         <f t="shared" ref="O3:O27" si="1">+N3*M3*L3</f>
         <v>6.9999999999999993E-2</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="Q3">
+        <f>+N3</f>
+        <v>0.35</v>
+      </c>
+      <c r="R3">
+        <f>+N4*M4</f>
+        <v>0.308</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>38</v>
       </c>
@@ -952,8 +962,16 @@
         <f t="shared" si="1"/>
         <v>6.1600000000000002E-2</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="Q4">
+        <f>1-M2</f>
+        <v>0.12</v>
+      </c>
+      <c r="R4">
+        <f>1-R3</f>
+        <v>0.69199999999999995</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
         <v>40</v>
       </c>
@@ -1002,7 +1020,7 @@
         <v>6.9999999999999993E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>23</v>
       </c>
@@ -1051,7 +1069,7 @@
         <v>0.11704000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
         <v>25</v>
       </c>
@@ -1100,7 +1118,7 @@
         <v>0.13299999999999998</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>41</v>
       </c>
@@ -1149,7 +1167,7 @@
         <v>0.11704000000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
         <v>42</v>
       </c>
@@ -1198,7 +1216,7 @@
         <v>0.13299999999999998</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>26</v>
       </c>
@@ -1247,7 +1265,7 @@
         <v>7.6999999999999999E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
         <v>29</v>
       </c>
@@ -1296,7 +1314,7 @@
         <v>8.7499999999999994E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
         <v>43</v>
       </c>
@@ -1345,7 +1363,7 @@
         <v>7.6999999999999999E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A13" s="7" t="s">
         <v>44</v>
       </c>
@@ -1394,7 +1412,7 @@
         <v>8.7499999999999994E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
         <v>30</v>
       </c>
@@ -1443,7 +1461,7 @@
         <v>3.0800000000000001E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A15" s="7" t="s">
         <v>34</v>
       </c>
@@ -1492,7 +1510,7 @@
         <v>3.4999999999999996E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>45</v>
       </c>

--- a/data/crops/lu_c_factor_reducedtillage.xlsx
+++ b/data/crops/lu_c_factor_reducedtillage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://worldwildlifefund-my.sharepoint.com/personal/cristobal_loyola_wwfus_org/Documents/Documents/203. Python projects/SBTN_Test/data/crops/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="86" documentId="8_{DE03094A-62C0-4937-830E-90DB4B2587C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A6D869F-5FC4-4115-A285-1B9618839F49}"/>
+  <xr:revisionPtr revIDLastSave="87" documentId="8_{DE03094A-62C0-4937-830E-90DB4B2587C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8F45275-9D2B-49CD-B7E4-0579DDDD1CA3}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{AD288E80-6FC1-4BDD-A593-FC9351635447}"/>
   </bookViews>
@@ -749,7 +749,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3D563D1-830A-486E-AE30-CC87FDA7651F}">
-  <dimension ref="A1:R27"/>
+  <dimension ref="A1:O27"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="49.453125" bestFit="1" customWidth="1"/>
@@ -761,7 +761,7 @@
     <col min="10" max="10" width="26.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -808,7 +808,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>13</v>
       </c>
@@ -857,7 +857,7 @@
         <v>6.1600000000000002E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" s="7" t="s">
         <v>21</v>
       </c>
@@ -905,16 +905,8 @@
         <f t="shared" ref="O3:O27" si="1">+N3*M3*L3</f>
         <v>6.9999999999999993E-2</v>
       </c>
-      <c r="Q3">
-        <f>+N3</f>
-        <v>0.35</v>
-      </c>
-      <c r="R3">
-        <f>+N4*M4</f>
-        <v>0.308</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>38</v>
       </c>
@@ -962,16 +954,8 @@
         <f t="shared" si="1"/>
         <v>6.1600000000000002E-2</v>
       </c>
-      <c r="Q4">
-        <f>1-M2</f>
-        <v>0.12</v>
-      </c>
-      <c r="R4">
-        <f>1-R3</f>
-        <v>0.69199999999999995</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
         <v>40</v>
       </c>
@@ -1020,7 +1004,7 @@
         <v>6.9999999999999993E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>23</v>
       </c>
@@ -1069,7 +1053,7 @@
         <v>0.11704000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
         <v>25</v>
       </c>
@@ -1118,7 +1102,7 @@
         <v>0.13299999999999998</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>41</v>
       </c>
@@ -1167,7 +1151,7 @@
         <v>0.11704000000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
         <v>42</v>
       </c>
@@ -1216,7 +1200,7 @@
         <v>0.13299999999999998</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>26</v>
       </c>
@@ -1265,7 +1249,7 @@
         <v>7.6999999999999999E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
         <v>29</v>
       </c>
@@ -1314,7 +1298,7 @@
         <v>8.7499999999999994E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
         <v>43</v>
       </c>
@@ -1363,7 +1347,7 @@
         <v>7.6999999999999999E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A13" s="7" t="s">
         <v>44</v>
       </c>
@@ -1412,7 +1396,7 @@
         <v>8.7499999999999994E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
         <v>30</v>
       </c>
@@ -1461,7 +1445,7 @@
         <v>3.0800000000000001E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A15" s="7" t="s">
         <v>34</v>
       </c>
@@ -1510,7 +1494,7 @@
         <v>3.4999999999999996E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>45</v>
       </c>
